--- a/Result/profitability/4138.xlsx
+++ b/Result/profitability/4138.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.72</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06625</v>
+        <v>1.025</v>
       </c>
       <c r="N2" t="n">
-        <v>43.18625</v>
+        <v>43.08625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9974999999999999</v>
+        <v>0.9149999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>42.07125</v>
+        <v>41.9325</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9125000000000001</v>
+        <v>0.8937499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>41.56625</v>
+        <v>41.92375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>0.86</v>
+        <v>0.855</v>
       </c>
       <c r="N5" t="n">
-        <v>40.64875</v>
+        <v>40.325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0.93875</v>
+        <v>0.94875</v>
       </c>
       <c r="N6" t="n">
-        <v>39.4975</v>
+        <v>39.35125</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9875</v>
+        <v>0.9962500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>39.22</v>
+        <v>39.09625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>1.085</v>
+        <v>1.10375</v>
       </c>
       <c r="N8" t="n">
-        <v>38.38375</v>
+        <v>38.7775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>344</v>
+      </c>
+      <c r="D71" t="n">
+        <v>194</v>
+      </c>
+      <c r="E71" t="n">
+        <v>150</v>
+      </c>
+      <c r="F71" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="G71" t="n">
+        <v>47</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>13.52%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>11</v>
+      </c>
+      <c r="J71" t="n">
+        <v>58</v>
+      </c>
+      <c r="K71" t="n">
+        <v>40</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>43.73125</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>3.149999999999999</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.07777777777777772</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-0.03883495145631066</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-2.590000000000003</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.05601211072664369</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
